--- a/generated/sources/reports/merchandising/FW26_NewIn_SellThrough_wk42_final.xlsx
+++ b/generated/sources/reports/merchandising/FW26_NewIn_SellThrough_wk42_final.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet name="Read me" sheetId="1" r:id="rId1"/>
     <sheet name="Style x Region" sheetId="2" r:id="rId2"/>
-    <sheet name="ILVARO pink Asia" sheetId="3" r:id="rId3"/>
+    <sheet name="IRIDIA pink Asia" sheetId="3" r:id="rId3"/>
     <sheet name="Region summary" sheetId="4" r:id="rId4"/>
-    <sheet name="POLARIS" sheetId="5" r:id="rId5"/>
+    <sheet name="ASTRA" sheetId="5" r:id="rId5"/>
     <sheet name="Store detail" sheetId="6" r:id="rId6"/>
     <sheet name="Highlights" sheetId="7" r:id="rId7"/>
   </sheets>
@@ -38,7 +38,7 @@
     <t>Units received = allocation at launch + DC replenishments with goods receipt posted.</t>
   </si>
   <si>
-    <t>Launch dates: Collection FW26 03/09/2026; Genius POLARIS 24/09/2026.</t>
+    <t>Launch dates: Collection FW26 03/09/2026; Couture ASTRA 24/09/2026.</t>
   </si>
   <si>
     <t>Not comparable with Finance/Regional sell-through on value (sales / sales + stock at retail).</t>
@@ -80,7 +80,7 @@
     <t>Δ WoW pp</t>
   </si>
   <si>
-    <t>AMBRINE</t>
+    <t>AMALIA</t>
   </si>
   <si>
     <t>CHOCOLATE</t>
@@ -98,13 +98,13 @@
     <t>BLACK</t>
   </si>
   <si>
-    <t>ARNEB</t>
+    <t>ARTEM</t>
   </si>
   <si>
     <t>NAVY</t>
   </si>
   <si>
-    <t>ILVARO</t>
+    <t>IRIDIA</t>
   </si>
   <si>
     <t>OFF-WHITE</t>
@@ -113,31 +113,31 @@
     <t>POWDER PINK</t>
   </si>
   <si>
-    <t>POLARIS BALACLAVA</t>
+    <t>ASTRA BALACLAVA</t>
   </si>
   <si>
     <t>WHITE</t>
   </si>
   <si>
-    <t>POLARIS CAPE</t>
+    <t>ASTRA CAPE</t>
   </si>
   <si>
-    <t>POLARIS OVERSIZED</t>
+    <t>ASTRA OVERSIZED</t>
   </si>
   <si>
     <t>LIGHT BLUE</t>
   </si>
   <si>
-    <t>ROSIERE</t>
+    <t>RIVIERA</t>
   </si>
   <si>
     <t>OLIVE</t>
   </si>
   <si>
-    <t>WOOL TURTLENECK</t>
+    <t>CASHMERE TURTLENECK</t>
   </si>
   <si>
-    <t>ILVARO 510 POWDER PINK - Asian stores</t>
+    <t>IRIDIA 510 POWDER PINK - Asian stores</t>
   </si>
   <si>
     <t>Store</t>
@@ -215,7 +215,7 @@
     <t>Region ST% = average of store sell-through.</t>
   </si>
   <si>
-    <t>Genius POLARIS - sell-through by sub-region (weighted), cut-off 18/10</t>
+    <t>Couture ASTRA - sell-through by sub-region (weighted), cut-off 18/10</t>
   </si>
   <si>
     <t>Sub-region</t>
@@ -395,19 +395,19 @@
     <t>ZRH01</t>
   </si>
   <si>
-    <t>ILVARO powder pink: Asian stores at 88% sell-through at W40 (core sizes sold out in 1-3 days after 02/10, only single pieces in fringe sizes 00/3/4 left). Top-up of 08/10 sold immediately in Asia; some EU/US stores still hold pink (Paris, Milano, New York).</t>
+    <t>IRIDIA powder pink: Asian stores at 88% sell-through at W40 (core sizes sold out in 1-3 days after 02/10, only single pieces in fringe sizes 00/3/4 left). Top-up of 08/10 sold immediately in Asia; some EU/US stores still hold pink (Paris, Milano, New York).</t>
   </si>
   <si>
-    <t>AMBRINE chocolate: EMEA sell-through 71% vs black 61%; sizes 0-1-2 broken, DC no stock until 10/11.</t>
+    <t>AMALIA chocolate: EMEA sell-through 71% vs black 61%; sizes 0-1-2 broken, DC no stock until 10/11.</t>
   </si>
   <si>
-    <t>POLARIS: Greater China well ahead of Europe and Americas - candidate for inter-region transfer.</t>
+    <t>ASTRA: Greater China well ahead of Europe and Americas - candidate for inter-region transfer.</t>
   </si>
   <si>
-    <t>ARNEB: ST inflated by size exchanges (exchange = return + new sale); net sell-through lower.</t>
+    <t>ARTEM: ST inflated by size exchanges (exchange = return + new sale); net sell-through lower.</t>
   </si>
   <si>
-    <t>WOOL TURTLENECK chocolate performing in line with black - brown trend confirmed.</t>
+    <t>CASHMERE TURTLENECK chocolate performing in line with black - brown trend confirmed.</t>
   </si>
 </sst>
 </file>
@@ -550,7 +550,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>POLARIS ST% by sub-region</a:t>
+              <a:t>ASTRA ST% by sub-region</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -579,7 +579,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>POLARIS!$A$4:$A$20</c:f>
+              <c:f>ASTRA!$A$4:$A$20</c:f>
               <c:strCache>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
@@ -638,7 +638,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>POLARIS!$D$4:$D$20</c:f>
+              <c:f>ASTRA!$D$4:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
